--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
     <sheet name="200126511" sheetId="2" r:id="rId2"/>
-    <sheet name="formula_page" sheetId="3" r:id="rId3"/>
+    <sheet name="200126512" sheetId="3" r:id="rId3"/>
+    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
   <si>
     <t>Date:</t>
   </si>
@@ -24,16 +25,16 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>100046511</t>
-  </si>
-  <si>
-    <t>other</t>
+    <t>100045486</t>
+  </si>
+  <si>
+    <t>Hotplate</t>
   </si>
   <si>
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Cr</t>
+    <t>Cr6</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -57,46 +58,22 @@
     <t>200126511_2</t>
   </si>
   <si>
-    <t>Cr2O3</t>
-  </si>
-  <si>
-    <t>Cr ICP analysis</t>
+    <t>200126512_1</t>
+  </si>
+  <si>
+    <t>200126512_2</t>
+  </si>
+  <si>
+    <t>Cr6 titration analysis</t>
   </si>
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>Dilution</t>
-  </si>
-  <si>
-    <t>conc. [mg/L]</t>
-  </si>
-  <si>
-    <t>Cr_ppm</t>
-  </si>
-  <si>
-    <t>%Cr</t>
-  </si>
-  <si>
-    <t>cr result:</t>
-  </si>
-  <si>
-    <t>cr oxide factor:</t>
-  </si>
-  <si>
-    <t>cr oxide result:</t>
-  </si>
-  <si>
-    <t>cr lot:</t>
-  </si>
-  <si>
-    <t>Cr2O3 titration analysis</t>
-  </si>
-  <si>
     <t>titrant_volume (mL)</t>
   </si>
   <si>
-    <t>%Cr2O3</t>
+    <t>%Cr6</t>
   </si>
   <si>
     <t>FAS:</t>
@@ -151,11 +128,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -233,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -247,18 +223,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -557,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -636,71 +610,26 @@
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -708,17 +637,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +654,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -734,18 +662,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>17</v>
@@ -753,235 +681,235 @@
       <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="5">
-        <f>"1/1"</f>
+        <f>G7</f>
         <v>0</v>
       </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="7">
-        <f>((C7)*(H7)*(I7))/(G7*1)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <f>D7/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="D7" s="5"/>
+      <c r="G7" s="7">
         <f>digestion_page!B10</f>
         <v>0</v>
       </c>
-      <c r="H7" s="8">
-        <f>digestion_page!C10</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <f>(LEFT(B7,FIND("/",B7)-1)/RIGHT(B7,LEN(B7)-FIND("/", B7)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5">
-        <f>"1/1"</f>
+        <f>G8</f>
         <v>0</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="7">
-        <f>((C8)*(H8)*(I8))/(G8*1)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <f>D8/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="D8" s="5"/>
+      <c r="G8" s="7">
         <f>digestion_page!B11</f>
         <v>0</v>
       </c>
-      <c r="H8" s="8">
-        <f>digestion_page!C11</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
-        <f>(LEFT(B8,FIND("/",B8)-1)/RIGHT(B8,LEN(B8)-FIND("/", B8)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="9" t="s">
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10">
-        <f>AVERAGE(D7:D8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="9" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="11">
-        <f>AVERAGE(E7:E8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="9" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="10">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="11">
-        <f>AVERAGE(E7:E8)*(C12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="5">
-        <f>G18</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="G18" s="8">
-        <f>digestion_page!B19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="5">
-        <f>G19</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="G19" s="8">
-        <f>digestion_page!B20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="6"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10">
-        <f>AVERAGE(D18:D19)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="11">
-        <f>AVERAGE(D18:D19)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C25:F27"/>
+    <mergeCell ref="C14:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="G7" s="7">
+        <f>digestion_page!B12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="G8" s="7">
+        <f>digestion_page!B13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C14:F16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -990,68 +918,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="14" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="14" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="14" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="14" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="12" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="14" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200126511" sheetId="2" r:id="rId2"/>
-    <sheet name="200126512" sheetId="3" r:id="rId3"/>
-    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
+    <sheet name="200127586" sheetId="2" r:id="rId2"/>
+    <sheet name="200127587" sheetId="3" r:id="rId3"/>
+    <sheet name="200127588" sheetId="4" r:id="rId4"/>
+    <sheet name="formula_page" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="103">
   <si>
     <t>Date:</t>
   </si>
@@ -25,55 +26,121 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>100045486</t>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Element(s)</t>
+  </si>
+  <si>
+    <t>Cr6</t>
+  </si>
+  <si>
+    <t>SOP#</t>
+  </si>
+  <si>
+    <t>Cocktail</t>
+  </si>
+  <si>
+    <t>sample(s)</t>
+  </si>
+  <si>
+    <t>weight (g)</t>
+  </si>
+  <si>
+    <t>volume (mL)</t>
+  </si>
+  <si>
+    <t>200127586_1</t>
+  </si>
+  <si>
+    <t>200127586_2</t>
+  </si>
+  <si>
+    <t>Microwave</t>
+  </si>
+  <si>
+    <t>Ca, Cu</t>
+  </si>
+  <si>
+    <t>Acid Cocktail</t>
+  </si>
+  <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Vessel</t>
+  </si>
+  <si>
+    <t>Stir</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>Power (W)</t>
+  </si>
+  <si>
+    <t>T1 (°C)</t>
+  </si>
+  <si>
+    <t>T2 (°C)</t>
+  </si>
+  <si>
+    <t>P (bar)</t>
+  </si>
+  <si>
+    <t>200127587_1</t>
+  </si>
+  <si>
+    <t>200127587_2</t>
+  </si>
+  <si>
+    <t>Katanax</t>
+  </si>
+  <si>
+    <t>Ti, Si</t>
+  </si>
+  <si>
+    <t>200127588_1</t>
+  </si>
+  <si>
+    <t>200127588_2</t>
   </si>
   <si>
     <t>Hotplate</t>
   </si>
   <si>
-    <t>Element(s)</t>
-  </si>
-  <si>
-    <t>Cr6</t>
-  </si>
-  <si>
-    <t>SOP#</t>
-  </si>
-  <si>
-    <t>Cocktail</t>
-  </si>
-  <si>
-    <t>sample(s)</t>
-  </si>
-  <si>
-    <t>weight (g)</t>
-  </si>
-  <si>
-    <t>volume (mL)</t>
-  </si>
-  <si>
-    <t>200126511_1</t>
-  </si>
-  <si>
-    <t>200126511_2</t>
-  </si>
-  <si>
-    <t>200126512_1</t>
-  </si>
-  <si>
-    <t>200126512_2</t>
+    <t>Ag, Pd</t>
+  </si>
+  <si>
+    <t>LOI temp:</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>crucible (g)</t>
+  </si>
+  <si>
+    <t>crucible + sample (g)</t>
+  </si>
+  <si>
+    <t>LOI (%)</t>
+  </si>
+  <si>
+    <t>correction</t>
+  </si>
+  <si>
+    <t>200127586</t>
   </si>
   <si>
     <t>Cr6 titration analysis</t>
   </si>
   <si>
-    <t>sample</t>
-  </si>
-  <si>
     <t>titrant_volume (mL)</t>
   </si>
   <si>
-    <t>%Cr6</t>
+    <t>%Cr6 [dried]</t>
   </si>
   <si>
     <t>FAS:</t>
@@ -82,7 +149,145 @@
     <t>reported result:</t>
   </si>
   <si>
+    <t>Ca ICP analysis</t>
+  </si>
+  <si>
+    <t>Dilution</t>
+  </si>
+  <si>
+    <t>conc. [mg/L]</t>
+  </si>
+  <si>
+    <t>Ca_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Ca [dried]</t>
+  </si>
+  <si>
+    <t>ca result:</t>
+  </si>
+  <si>
+    <t>ca oxide factor:</t>
+  </si>
+  <si>
+    <t>ca oxide result:</t>
+  </si>
+  <si>
+    <t>ca lot:</t>
+  </si>
+  <si>
+    <t>Cu ICP analysis</t>
+  </si>
+  <si>
+    <t>Cu_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Cu [dried]</t>
+  </si>
+  <si>
+    <t>cu result:</t>
+  </si>
+  <si>
+    <t>cu oxide factor:</t>
+  </si>
+  <si>
+    <t>cu oxide result:</t>
+  </si>
+  <si>
+    <t>cu lot:</t>
+  </si>
+  <si>
+    <t>Ag ICP analysis</t>
+  </si>
+  <si>
+    <t>Ag_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Ag [dried]</t>
+  </si>
+  <si>
+    <t>ag result:</t>
+  </si>
+  <si>
+    <t>ag oxide factor:</t>
+  </si>
+  <si>
+    <t>ag oxide result:</t>
+  </si>
+  <si>
+    <t>ag lot:</t>
+  </si>
+  <si>
+    <t>Pd ICP analysis</t>
+  </si>
+  <si>
+    <t>Pd_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Pd [dried]</t>
+  </si>
+  <si>
+    <t>pd result:</t>
+  </si>
+  <si>
+    <t>pd oxide factor:</t>
+  </si>
+  <si>
+    <t>pd oxide result:</t>
+  </si>
+  <si>
+    <t>pd lot:</t>
+  </si>
+  <si>
     <t>Note(s):</t>
+  </si>
+  <si>
+    <t>200127587</t>
+  </si>
+  <si>
+    <t>Ti ICP analysis</t>
+  </si>
+  <si>
+    <t>Ti_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Ti [dried]</t>
+  </si>
+  <si>
+    <t>ti result:</t>
+  </si>
+  <si>
+    <t>ti oxide factor:</t>
+  </si>
+  <si>
+    <t>ti oxide result:</t>
+  </si>
+  <si>
+    <t>ti lot:</t>
+  </si>
+  <si>
+    <t>Si ICP analysis</t>
+  </si>
+  <si>
+    <t>Si_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Si [dried]</t>
+  </si>
+  <si>
+    <t>si result:</t>
+  </si>
+  <si>
+    <t>si oxide factor:</t>
+  </si>
+  <si>
+    <t>si oxide result:</t>
+  </si>
+  <si>
+    <t>si lot:</t>
+  </si>
+  <si>
+    <t>200127588</t>
   </si>
   <si>
     <t>A = crucible</t>
@@ -128,10 +333,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -209,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -220,19 +427,25 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -531,15 +744,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,89 +762,384 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>100482511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5">
+        <v>15</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C22" s="5">
+        <v>180</v>
+      </c>
+      <c r="D22" s="5">
+        <v>65</v>
+      </c>
+      <c r="E22" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5">
+        <v>1500</v>
+      </c>
+      <c r="C23" s="5">
+        <v>240</v>
+      </c>
+      <c r="D23" s="5">
+        <v>65</v>
+      </c>
+      <c r="E23" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="19">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -637,13 +1147,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -658,115 +1170,705 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>100482511</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6"/>
+      <c r="A5" s="7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5">
-        <f>G7</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="G7" s="7">
+      <c r="E7" s="8">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <f>G11</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="G11" s="11">
         <f>digestion_page!B10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="7">
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <f>G12</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="G12" s="11">
         <f>digestion_page!B11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="10">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="14" spans="1:7">
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="12">
+        <f>AVERAGE(D11:D12)*(10000)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="A16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="13">
+        <f>AVERAGE(D11:D12)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="8">
+        <f>((C20)*(H20)*(I20))/(G20*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="8">
+        <f>D20/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="11">
+        <f>digestion_page!B26</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <f>digestion_page!C26</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <f>(LEFT(B20,FIND("/",B20)-1)/RIGHT(B20,LEN(B20)-FIND("/", B20)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="8">
+        <f>((C21)*(H21)*(I21))/(G21*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <f>D21/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="11">
+        <f>digestion_page!B27</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
+        <f>digestion_page!C27</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <f>(LEFT(B21,FIND("/",B21)-1)/RIGHT(B21,LEN(B21)-FIND("/", B21)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="12">
+        <f>AVERAGE(D20:D21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="13">
+        <f>AVERAGE(E20:E21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="10"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="13">
+        <f>AVERAGE(E20:E21)*(C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="10"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="8">
+        <f>((C31)*(H31)*(I31))/(G31*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <f>D31/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="11">
+        <f>digestion_page!B26</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <f>digestion_page!C26</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="11">
+        <f>(LEFT(B31,FIND("/",B31)-1)/RIGHT(B31,LEN(B31)-FIND("/", B31)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="8">
+        <f>((C32)*(H32)*(I32))/(G32*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <f>D32/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="11">
+        <f>digestion_page!B27</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="11">
+        <f>digestion_page!C27</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="11">
+        <f>(LEFT(B32,FIND("/",B32)-1)/RIGHT(B32,LEN(B32)-FIND("/", B32)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="12">
+        <f>AVERAGE(D31:D32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="13">
+        <f>AVERAGE(E31:E32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="10"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="13">
+        <f>AVERAGE(E31:E32)*(C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="10"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="8">
+        <f>((C42)*(H42)*(I42))/(G42*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="8">
+        <f>D42/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="11">
+        <f>digestion_page!B48</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="11">
+        <f>digestion_page!C48</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11">
+        <f>(LEFT(B42,FIND("/",B42)-1)/RIGHT(B42,LEN(B42)-FIND("/", B42)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="8">
+        <f>((C43)*(H43)*(I43))/(G43*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="8">
+        <f>D43/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="11">
+        <f>digestion_page!B49</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="11">
+        <f>digestion_page!C49</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11">
+        <f>(LEFT(B43,FIND("/",B43)-1)/RIGHT(B43,LEN(B43)-FIND("/", B43)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="12">
+        <f>AVERAGE(D42:D43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="13">
+        <f>AVERAGE(E42:E43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="10"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="13">
+        <f>AVERAGE(E42:E43)*(C47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="10"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="8">
+        <f>((C53)*(H53)*(I53))/(G53*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <f>D53/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="11">
+        <f>digestion_page!B48</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="11">
+        <f>digestion_page!C48</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <f>(LEFT(B53,FIND("/",B53)-1)/RIGHT(B53,LEN(B53)-FIND("/", B53)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="8">
+        <f>((C54)*(H54)*(I54))/(G54*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="8">
+        <f>D54/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="11">
+        <f>digestion_page!B49</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="11">
+        <f>digestion_page!C49</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="11">
+        <f>(LEFT(B54,FIND("/",B54)-1)/RIGHT(B54,LEN(B54)-FIND("/", B54)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="12">
+        <f>AVERAGE(D53:D54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="13">
+        <f>AVERAGE(E53:E54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="13">
+        <f>AVERAGE(E53:E54)*(C58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="B62" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
+  <mergeCells count="33">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C62:F64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -774,16 +1876,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -791,125 +1895,1008 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="B2">
+        <v>100482511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="5">
-        <f>G7</f>
-        <v>0</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="G7" s="7">
-        <f>digestion_page!B12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="7">
-        <f>digestion_page!B13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="10">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="E7" s="8">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="8">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <f>digestion_page!B28</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <f>digestion_page!C28</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="8">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <f>digestion_page!B29</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <f>digestion_page!C29</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="12">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="13">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="13">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="10"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <f>digestion_page!B28</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <f>digestion_page!C28</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
+        <f>digestion_page!B29</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <f>digestion_page!C29</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="12">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="13">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="13">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="8">
+        <f>((C33)*(H33)*(I33))/(G33*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <f>D33/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="11">
+        <f>digestion_page!B37</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <f>digestion_page!C37</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <f>(LEFT(B33,FIND("/",B33)-1)/RIGHT(B33,LEN(B33)-FIND("/", B33)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="8">
+        <f>((C34)*(H34)*(I34))/(G34*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
+        <f>D34/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="11">
+        <f>digestion_page!B38</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <f>digestion_page!C38</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="11">
+        <f>(LEFT(B34,FIND("/",B34)-1)/RIGHT(B34,LEN(B34)-FIND("/", B34)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="12">
+        <f>AVERAGE(D33:D34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="13">
+        <f>AVERAGE(E33:E34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="10"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="13">
+        <f>AVERAGE(E33:E34)*(C38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="10"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="8">
+        <f>((C44)*(H44)*(I44))/(G44*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="8">
+        <f>D44/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="11">
+        <f>digestion_page!B37</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="11">
+        <f>digestion_page!C37</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="11">
+        <f>(LEFT(B44,FIND("/",B44)-1)/RIGHT(B44,LEN(B44)-FIND("/", B44)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="8">
+        <f>((C45)*(H45)*(I45))/(G45*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="8">
+        <f>D45/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="11">
+        <f>digestion_page!B38</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <f>digestion_page!C38</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="11">
+        <f>(LEFT(B45,FIND("/",B45)-1)/RIGHT(B45,LEN(B45)-FIND("/", B45)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="12">
+        <f>AVERAGE(D44:D45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="13">
+        <f>AVERAGE(E44:E45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="10"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="13">
+        <f>AVERAGE(E44:E45)*(C49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="B53" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
+  <mergeCells count="29">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C53:F55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>100482511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="8">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="8">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <f>digestion_page!B39</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <f>digestion_page!C39</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="8">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <f>digestion_page!B40</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <f>digestion_page!C40</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="12">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="13">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="13">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="10"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <f>digestion_page!B39</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <f>digestion_page!C39</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
+        <f>digestion_page!B40</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <f>digestion_page!C40</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="12">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="13">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="13">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -918,68 +2905,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
-        <v>22</v>
+      <c r="A1" s="16" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12" t="s">
-        <v>23</v>
+      <c r="A2" s="16" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="12" t="s">
-        <v>24</v>
+      <c r="A3" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="12" t="s">
-        <v>25</v>
+      <c r="A5" s="16" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="12" t="s">
-        <v>26</v>
+      <c r="A7" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
+      <c r="A9" s="16" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="12" t="s">
-        <v>28</v>
+      <c r="A11" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
+      <c r="A13" s="16" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="12" t="s">
-        <v>30</v>
+      <c r="A15" s="16" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="12" t="s">
-        <v>31</v>
+      <c r="A17" s="16" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="12" t="s">
-        <v>32</v>
+      <c r="A19" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="12" t="s">
-        <v>33</v>
+      <c r="A21" s="16" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="12" t="s">
-        <v>34</v>
+      <c r="A23" s="16" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="96">
   <si>
     <t>Date:</t>
   </si>
@@ -26,93 +26,87 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>other</t>
+    <t>Microwave</t>
   </si>
   <si>
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Cr6</t>
+    <t>Ca, Cu</t>
   </si>
   <si>
     <t>SOP#</t>
   </si>
   <si>
+    <t>Acid Cocktail</t>
+  </si>
+  <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Vessel</t>
+  </si>
+  <si>
+    <t>Stir</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>Power (W)</t>
+  </si>
+  <si>
+    <t>T1 (°C)</t>
+  </si>
+  <si>
+    <t>T2 (°C)</t>
+  </si>
+  <si>
+    <t>P (bar)</t>
+  </si>
+  <si>
+    <t>sample(s)</t>
+  </si>
+  <si>
+    <t>weight (g)</t>
+  </si>
+  <si>
+    <t>volume (mL)</t>
+  </si>
+  <si>
+    <t>200127586_1</t>
+  </si>
+  <si>
+    <t>200127586_2</t>
+  </si>
+  <si>
+    <t>200127587_1</t>
+  </si>
+  <si>
+    <t>200127587_2</t>
+  </si>
+  <si>
+    <t>Katanax</t>
+  </si>
+  <si>
+    <t>Ti, Si</t>
+  </si>
+  <si>
+    <t>200127588_1</t>
+  </si>
+  <si>
+    <t>200127588_2</t>
+  </si>
+  <si>
+    <t>Hotplate</t>
+  </si>
+  <si>
+    <t>Ag, Pd</t>
+  </si>
+  <si>
     <t>Cocktail</t>
   </si>
   <si>
-    <t>sample(s)</t>
-  </si>
-  <si>
-    <t>weight (g)</t>
-  </si>
-  <si>
-    <t>volume (mL)</t>
-  </si>
-  <si>
-    <t>200127586_1</t>
-  </si>
-  <si>
-    <t>200127586_2</t>
-  </si>
-  <si>
-    <t>Microwave</t>
-  </si>
-  <si>
-    <t>Ca, Cu</t>
-  </si>
-  <si>
-    <t>Acid Cocktail</t>
-  </si>
-  <si>
-    <t>Rack</t>
-  </si>
-  <si>
-    <t>Vessel</t>
-  </si>
-  <si>
-    <t>Stir</t>
-  </si>
-  <si>
-    <t>Time (min)</t>
-  </si>
-  <si>
-    <t>Power (W)</t>
-  </si>
-  <si>
-    <t>T1 (°C)</t>
-  </si>
-  <si>
-    <t>T2 (°C)</t>
-  </si>
-  <si>
-    <t>P (bar)</t>
-  </si>
-  <si>
-    <t>200127587_1</t>
-  </si>
-  <si>
-    <t>200127587_2</t>
-  </si>
-  <si>
-    <t>Katanax</t>
-  </si>
-  <si>
-    <t>Ti, Si</t>
-  </si>
-  <si>
-    <t>200127588_1</t>
-  </si>
-  <si>
-    <t>200127588_2</t>
-  </si>
-  <si>
-    <t>Hotplate</t>
-  </si>
-  <si>
-    <t>Ag, Pd</t>
-  </si>
-  <si>
     <t>LOI temp:</t>
   </si>
   <si>
@@ -132,21 +126,6 @@
   </si>
   <si>
     <t>200127586</t>
-  </si>
-  <si>
-    <t>Cr6 titration analysis</t>
-  </si>
-  <si>
-    <t>titrant_volume (mL)</t>
-  </si>
-  <si>
-    <t>%Cr6 [dried]</t>
-  </si>
-  <si>
-    <t>FAS:</t>
-  </si>
-  <si>
-    <t>reported result:</t>
   </si>
   <si>
     <t>Ca ICP analysis</t>
@@ -744,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -759,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -776,6 +755,8 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
@@ -785,6 +766,8 @@
         <v>4</v>
       </c>
       <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
@@ -792,6 +775,8 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
@@ -799,347 +784,282 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C13" s="5">
+        <v>180</v>
+      </c>
+      <c r="D13" s="5">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5">
+        <v>110</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="A14" s="5">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1500</v>
+      </c>
+      <c r="C14" s="5">
+        <v>240</v>
+      </c>
+      <c r="D14" s="5">
+        <v>65</v>
+      </c>
+      <c r="E14" s="5">
+        <v>110</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5">
+        <v>19</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5">
-        <v>15</v>
-      </c>
-      <c r="B22" s="5">
-        <v>1200</v>
-      </c>
-      <c r="C22" s="5">
-        <v>180</v>
-      </c>
-      <c r="D22" s="5">
-        <v>65</v>
-      </c>
-      <c r="E22" s="5">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5">
-        <v>1500</v>
-      </c>
-      <c r="C23" s="5">
-        <v>240</v>
-      </c>
-      <c r="D23" s="5">
-        <v>65</v>
-      </c>
-      <c r="E23" s="5">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="C28" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="5">
-        <v>250</v>
-      </c>
+      <c r="C37" s="5"/>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5">
-        <v>250</v>
+        <v>15</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="5">
-        <v>250</v>
-      </c>
+      <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="5">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="5"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
+      <c r="C40" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+  <mergeCells count="15">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1147,10 +1067,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -1158,15 +1078,15 @@
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1174,35 +1094,35 @@
         <v>100482511</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="4">
         <f>"after "&amp;B5&amp;" °C"</f>
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1216,659 +1136,578 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="10"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B11" s="5">
-        <f>G11</f>
+        <f>"1/1"</f>
         <v>0</v>
       </c>
       <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="D11" s="8">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
       <c r="G11" s="11">
-        <f>digestion_page!B10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <f>digestion_page!B17</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <f>digestion_page!C17</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5">
-        <f>G12</f>
+        <f>"1/1"</f>
         <v>0</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="D12" s="8">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
       <c r="G12" s="11">
-        <f>digestion_page!B11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <f>digestion_page!B18</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <f>digestion_page!C18</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="10"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="C14" s="12">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="12">
-        <f>AVERAGE(D11:D12)*(10000)*(1/$F$7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="C15" s="13">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="13">
-        <f>AVERAGE(D11:D12)*(1/$F$7)</f>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="13">
+        <f>AVERAGE(E11:E12)*(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="10"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="5">
-        <f>"1/1"</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="8">
-        <f>((C20)*(H20)*(I20))/(G20*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
-        <f>D20/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="11">
-        <f>digestion_page!B26</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="11">
-        <f>digestion_page!C26</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="11">
-        <f>(LEFT(B20,FIND("/",B20)-1)/RIGHT(B20,LEN(B20)-FIND("/", B20)))</f>
-        <v>0</v>
-      </c>
+      <c r="B20" s="10"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="5">
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="8">
-        <f>((C21)*(H21)*(I21))/(G21*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <f>D21/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="11">
-        <f>digestion_page!B27</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="11">
-        <f>digestion_page!C27</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="11">
-        <f>(LEFT(B21,FIND("/",B21)-1)/RIGHT(B21,LEN(B21)-FIND("/", B21)))</f>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <f>digestion_page!B17</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <f>digestion_page!C17</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="12">
-        <f>AVERAGE(D20:D21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="13">
-        <f>AVERAGE(E20:E21)</f>
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
+        <f>digestion_page!B18</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <f>digestion_page!C18</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="7"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="12">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="13">
-        <f>AVERAGE(E20:E21)*(C25)</f>
+        <f>AVERAGE(E22:E23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="13">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="10" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="10"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="5">
-        <f>"1/1"</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="8">
-        <f>((C31)*(H31)*(I31))/(G31*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
-        <f>D31/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="11">
-        <f>digestion_page!B26</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="11">
-        <f>digestion_page!C26</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="11">
-        <f>(LEFT(B31,FIND("/",B31)-1)/RIGHT(B31,LEN(B31)-FIND("/", B31)))</f>
-        <v>0</v>
-      </c>
+      <c r="B31" s="10"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="5">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="5">
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="8">
-        <f>((C32)*(H32)*(I32))/(G32*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="8">
-        <f>D32/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="11">
-        <f>digestion_page!B27</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="11">
-        <f>digestion_page!C27</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="11">
-        <f>(LEFT(B32,FIND("/",B32)-1)/RIGHT(B32,LEN(B32)-FIND("/", B32)))</f>
+      <c r="C33" s="5"/>
+      <c r="D33" s="8">
+        <f>((C33)*(H33)*(I33))/(G33*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <f>D33/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="11">
+        <f>digestion_page!B39</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <f>digestion_page!C39</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <f>(LEFT(B33,FIND("/",B33)-1)/RIGHT(B33,LEN(B33)-FIND("/", B33)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="12">
-        <f>AVERAGE(D31:D32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="13">
-        <f>AVERAGE(E31:E32)</f>
+      <c r="A34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="8">
+        <f>((C34)*(H34)*(I34))/(G34*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
+        <f>D34/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="11">
+        <f>digestion_page!B40</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <f>digestion_page!C40</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="11">
+        <f>(LEFT(B34,FIND("/",B34)-1)/RIGHT(B34,LEN(B34)-FIND("/", B34)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" s="7"/>
-      <c r="C36" s="10"/>
+      <c r="C36" s="12">
+        <f>AVERAGE(D33:D34)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="13">
-        <f>AVERAGE(E31:E32)*(C36)</f>
+        <f>AVERAGE(E33:E34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="10"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="13">
+        <f>AVERAGE(E33:E34)*(C38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="10" t="s">
+      <c r="B40" s="7"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="10"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="5">
-        <f>"1/1"</f>
-        <v>0</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="8">
-        <f>((C42)*(H42)*(I42))/(G42*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="8">
-        <f>D42/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="11">
-        <f>digestion_page!B48</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="11">
-        <f>digestion_page!C48</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11">
-        <f>(LEFT(B42,FIND("/",B42)-1)/RIGHT(B42,LEN(B42)-FIND("/", B42)))</f>
-        <v>0</v>
-      </c>
+      <c r="B42" s="10"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="5">
+        <v>30</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="5">
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="8">
-        <f>((C43)*(H43)*(I43))/(G43*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="8">
-        <f>D43/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="11">
-        <f>digestion_page!B49</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="11">
-        <f>digestion_page!C49</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="11">
-        <f>(LEFT(B43,FIND("/",B43)-1)/RIGHT(B43,LEN(B43)-FIND("/", B43)))</f>
+      <c r="C44" s="5"/>
+      <c r="D44" s="8">
+        <f>((C44)*(H44)*(I44))/(G44*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="8">
+        <f>D44/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="11">
+        <f>digestion_page!B39</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="11">
+        <f>digestion_page!C39</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="11">
+        <f>(LEFT(B44,FIND("/",B44)-1)/RIGHT(B44,LEN(B44)-FIND("/", B44)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="12">
-        <f>AVERAGE(D42:D43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="13">
-        <f>AVERAGE(E42:E43)</f>
+      <c r="A45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="8">
+        <f>((C45)*(H45)*(I45))/(G45*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="8">
+        <f>D45/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="11">
+        <f>digestion_page!B40</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <f>digestion_page!C40</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="11">
+        <f>(LEFT(B45,FIND("/",B45)-1)/RIGHT(B45,LEN(B45)-FIND("/", B45)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B47" s="7"/>
-      <c r="C47" s="10"/>
+      <c r="C47" s="12">
+        <f>AVERAGE(D44:D45)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="13">
-        <f>AVERAGE(E42:E43)*(C47)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <f>AVERAGE(E44:E45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="10"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="13">
+        <f>AVERAGE(E44:E45)*(C49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="10" t="s">
+      <c r="B51" s="7"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="B53" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B51" s="10"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="5">
-        <f>"1/1"</f>
-        <v>0</v>
-      </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="8">
-        <f>((C53)*(H53)*(I53))/(G53*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="8">
-        <f>D53/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="11">
-        <f>digestion_page!B48</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="11">
-        <f>digestion_page!C48</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="11">
-        <f>(LEFT(B53,FIND("/",B53)-1)/RIGHT(B53,LEN(B53)-FIND("/", B53)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="5">
-        <f>"1/1"</f>
-        <v>0</v>
-      </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="8">
-        <f>((C54)*(H54)*(I54))/(G54*$F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="8">
-        <f>D54/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="11">
-        <f>digestion_page!B49</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="11">
-        <f>digestion_page!C49</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="11">
-        <f>(LEFT(B54,FIND("/",B54)-1)/RIGHT(B54,LEN(B54)-FIND("/", B54)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="12">
-        <f>AVERAGE(D53:D54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="13">
-        <f>AVERAGE(E53:E54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="10"/>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="13">
-        <f>AVERAGE(E53:E54)*(C58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="B62" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="29">
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C62:F64"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C53:F55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1892,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1905,33 +1744,33 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="4">
         <f>"after "&amp;B5&amp;" °C"</f>
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1947,30 +1786,30 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5">
         <f>"1/1"</f>
@@ -1986,11 +1825,11 @@
         <v>0</v>
       </c>
       <c r="G11" s="11">
-        <f>digestion_page!B28</f>
+        <f>digestion_page!B19</f>
         <v>0</v>
       </c>
       <c r="H11" s="11">
-        <f>digestion_page!C28</f>
+        <f>digestion_page!C19</f>
         <v>0</v>
       </c>
       <c r="I11" s="11">
@@ -2000,7 +1839,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5">
         <f>"1/1"</f>
@@ -2016,11 +1855,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="11">
-        <f>digestion_page!B29</f>
+        <f>digestion_page!B20</f>
         <v>0</v>
       </c>
       <c r="H12" s="11">
-        <f>digestion_page!C29</f>
+        <f>digestion_page!C20</f>
         <v>0</v>
       </c>
       <c r="I12" s="11">
@@ -2030,7 +1869,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12">
@@ -2040,7 +1879,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="13">
@@ -2050,14 +1889,14 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="13">
@@ -2067,7 +1906,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="14"/>
@@ -2077,30 +1916,30 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="10" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B20" s="10"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B22" s="5">
         <f>"1/1"</f>
@@ -2116,11 +1955,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="11">
-        <f>digestion_page!B28</f>
+        <f>digestion_page!B19</f>
         <v>0</v>
       </c>
       <c r="H22" s="11">
-        <f>digestion_page!C28</f>
+        <f>digestion_page!C19</f>
         <v>0</v>
       </c>
       <c r="I22" s="11">
@@ -2130,7 +1969,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5">
         <f>"1/1"</f>
@@ -2146,11 +1985,11 @@
         <v>0</v>
       </c>
       <c r="G23" s="11">
-        <f>digestion_page!B29</f>
+        <f>digestion_page!B20</f>
         <v>0</v>
       </c>
       <c r="H23" s="11">
-        <f>digestion_page!C29</f>
+        <f>digestion_page!C20</f>
         <v>0</v>
       </c>
       <c r="I23" s="11">
@@ -2160,7 +1999,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12">
@@ -2170,7 +2009,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="13">
@@ -2180,14 +2019,14 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="13">
@@ -2197,7 +2036,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="14"/>
@@ -2207,30 +2046,30 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B31" s="10"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B33" s="5">
         <f>"1/1"</f>
@@ -2246,11 +2085,11 @@
         <v>0</v>
       </c>
       <c r="G33" s="11">
-        <f>digestion_page!B37</f>
+        <f>digestion_page!B28</f>
         <v>0</v>
       </c>
       <c r="H33" s="11">
-        <f>digestion_page!C37</f>
+        <f>digestion_page!C28</f>
         <v>0</v>
       </c>
       <c r="I33" s="11">
@@ -2260,7 +2099,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B34" s="5">
         <f>"1/1"</f>
@@ -2276,11 +2115,11 @@
         <v>0</v>
       </c>
       <c r="G34" s="11">
-        <f>digestion_page!B38</f>
+        <f>digestion_page!B29</f>
         <v>0</v>
       </c>
       <c r="H34" s="11">
-        <f>digestion_page!C38</f>
+        <f>digestion_page!C29</f>
         <v>0</v>
       </c>
       <c r="I34" s="11">
@@ -2290,7 +2129,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="12">
@@ -2300,7 +2139,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="13">
@@ -2310,14 +2149,14 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="10"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="7" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="13">
@@ -2327,7 +2166,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="14"/>
@@ -2337,30 +2176,30 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B42" s="10"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B44" s="5">
         <f>"1/1"</f>
@@ -2376,11 +2215,11 @@
         <v>0</v>
       </c>
       <c r="G44" s="11">
-        <f>digestion_page!B37</f>
+        <f>digestion_page!B28</f>
         <v>0</v>
       </c>
       <c r="H44" s="11">
-        <f>digestion_page!C37</f>
+        <f>digestion_page!C28</f>
         <v>0</v>
       </c>
       <c r="I44" s="11">
@@ -2390,7 +2229,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B45" s="5">
         <f>"1/1"</f>
@@ -2406,11 +2245,11 @@
         <v>0</v>
       </c>
       <c r="G45" s="11">
-        <f>digestion_page!B38</f>
+        <f>digestion_page!B29</f>
         <v>0</v>
       </c>
       <c r="H45" s="11">
-        <f>digestion_page!C38</f>
+        <f>digestion_page!C29</f>
         <v>0</v>
       </c>
       <c r="I45" s="11">
@@ -2420,7 +2259,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="12">
@@ -2430,7 +2269,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="13">
@@ -2440,14 +2279,14 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="13">
@@ -2457,7 +2296,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="14"/>
@@ -2467,7 +2306,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="B53" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
@@ -2540,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2553,33 +2392,33 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="4">
         <f>"after "&amp;B5&amp;" °C"</f>
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2595,30 +2434,30 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5">
         <f>"1/1"</f>
@@ -2634,11 +2473,11 @@
         <v>0</v>
       </c>
       <c r="G11" s="11">
-        <f>digestion_page!B39</f>
+        <f>digestion_page!B30</f>
         <v>0</v>
       </c>
       <c r="H11" s="11">
-        <f>digestion_page!C39</f>
+        <f>digestion_page!C30</f>
         <v>0</v>
       </c>
       <c r="I11" s="11">
@@ -2648,7 +2487,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5">
         <f>"1/1"</f>
@@ -2664,11 +2503,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="11">
-        <f>digestion_page!B40</f>
+        <f>digestion_page!B31</f>
         <v>0</v>
       </c>
       <c r="H12" s="11">
-        <f>digestion_page!C40</f>
+        <f>digestion_page!C31</f>
         <v>0</v>
       </c>
       <c r="I12" s="11">
@@ -2678,7 +2517,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12">
@@ -2688,7 +2527,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="13">
@@ -2698,14 +2537,14 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="13">
@@ -2715,7 +2554,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="14"/>
@@ -2725,30 +2564,30 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B20" s="10"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B22" s="5">
         <f>"1/1"</f>
@@ -2764,11 +2603,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="11">
-        <f>digestion_page!B39</f>
+        <f>digestion_page!B30</f>
         <v>0</v>
       </c>
       <c r="H22" s="11">
-        <f>digestion_page!C39</f>
+        <f>digestion_page!C30</f>
         <v>0</v>
       </c>
       <c r="I22" s="11">
@@ -2778,7 +2617,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B23" s="5">
         <f>"1/1"</f>
@@ -2794,11 +2633,11 @@
         <v>0</v>
       </c>
       <c r="G23" s="11">
-        <f>digestion_page!B40</f>
+        <f>digestion_page!B31</f>
         <v>0</v>
       </c>
       <c r="H23" s="11">
-        <f>digestion_page!C40</f>
+        <f>digestion_page!C31</f>
         <v>0</v>
       </c>
       <c r="I23" s="11">
@@ -2808,7 +2647,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12">
@@ -2818,7 +2657,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="13">
@@ -2828,14 +2667,14 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="13">
@@ -2845,7 +2684,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="14"/>
@@ -2855,7 +2694,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
@@ -2906,67 +2745,67 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="16" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="16" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="16" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="16" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="16" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="16" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -312,12 +312,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="######&quot; °C&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -395,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -409,19 +411,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -433,7 +437,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -738,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -887,28 +899,28 @@
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="5"/>
     </row>
     <row r="23" spans="1:3">
@@ -956,7 +968,7 @@
       <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="5"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="5">
         <v>250</v>
       </c>
@@ -965,7 +977,7 @@
       <c r="A29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="5"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="5">
         <v>250</v>
       </c>
@@ -974,7 +986,7 @@
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="5"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="5">
         <v>250</v>
       </c>
@@ -983,7 +995,7 @@
       <c r="A31" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="5"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="5">
         <v>250</v>
       </c>
@@ -1033,14 +1045,14 @@
       <c r="A39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="5"/>
+      <c r="B39" s="7"/>
       <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="5"/>
+      <c r="B40" s="7"/>
       <c r="C40" s="5"/>
     </row>
   </sheetData>
@@ -1083,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1095,9 +1107,10 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
@@ -1127,20 +1140,20 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="8">
+      <c r="E7" s="10">
         <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
         <v>0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <f>1-(E7/100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
@@ -1167,24 +1180,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="8">
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
         <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="10">
         <f>D11/10000</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="13">
         <f>digestion_page!B17</f>
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="13">
         <f>digestion_page!C17</f>
         <v>0</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="13">
         <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
         <v>0</v>
       </c>
@@ -1197,80 +1210,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="8">
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
         <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="10">
         <f>D12/10000</f>
         <v>0</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="13">
         <f>digestion_page!B18</f>
         <v>0</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="13">
         <f>digestion_page!C18</f>
         <v>0</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="13">
         <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="12">
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
         <f>AVERAGE(D11:D12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="13">
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
         <f>AVERAGE(E11:E12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="13">
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
         <f>AVERAGE(E11:E12)*(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
@@ -1297,24 +1310,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8">
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
         <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="10">
         <f>D22/10000</f>
         <v>0</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="13">
         <f>digestion_page!B17</f>
         <v>0</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="13">
         <f>digestion_page!C17</f>
         <v>0</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="13">
         <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
         <v>0</v>
       </c>
@@ -1327,80 +1340,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8">
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
         <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="10">
         <f>D23/10000</f>
         <v>0</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="13">
         <f>digestion_page!B18</f>
         <v>0</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="13">
         <f>digestion_page!C18</f>
         <v>0</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="13">
         <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="12">
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
         <f>AVERAGE(D22:D23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="13">
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
         <f>AVERAGE(E22:E23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="10"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="13">
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
         <f>AVERAGE(E22:E23)*(C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="11"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
@@ -1427,24 +1440,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="8">
+      <c r="C33" s="12"/>
+      <c r="D33" s="10">
         <f>((C33)*(H33)*(I33))/(G33*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="10">
         <f>D33/10000</f>
         <v>0</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="13">
         <f>digestion_page!B39</f>
         <v>0</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="13">
         <f>digestion_page!C39</f>
         <v>0</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="13">
         <f>(LEFT(B33,FIND("/",B33)-1)/RIGHT(B33,LEN(B33)-FIND("/", B33)))</f>
         <v>0</v>
       </c>
@@ -1457,80 +1470,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="8">
+      <c r="C34" s="12"/>
+      <c r="D34" s="10">
         <f>((C34)*(H34)*(I34))/(G34*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="10">
         <f>D34/10000</f>
         <v>0</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="13">
         <f>digestion_page!B40</f>
         <v>0</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="13">
         <f>digestion_page!C40</f>
         <v>0</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="13">
         <f>(LEFT(B34,FIND("/",B34)-1)/RIGHT(B34,LEN(B34)-FIND("/", B34)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="12">
+      <c r="B36" s="8"/>
+      <c r="C36" s="14">
         <f>AVERAGE(D33:D34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="13">
+      <c r="B37" s="8"/>
+      <c r="C37" s="15">
         <f>AVERAGE(E33:E34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="10"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="13">
+      <c r="B39" s="8"/>
+      <c r="C39" s="15">
         <f>AVERAGE(E33:E34)*(C38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="10"/>
+      <c r="B42" s="11"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
@@ -1557,24 +1570,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="8">
+      <c r="C44" s="12"/>
+      <c r="D44" s="10">
         <f>((C44)*(H44)*(I44))/(G44*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="10">
         <f>D44/10000</f>
         <v>0</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="13">
         <f>digestion_page!B39</f>
         <v>0</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="13">
         <f>digestion_page!C39</f>
         <v>0</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="13">
         <f>(LEFT(B44,FIND("/",B44)-1)/RIGHT(B44,LEN(B44)-FIND("/", B44)))</f>
         <v>0</v>
       </c>
@@ -1587,95 +1600,95 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="8">
+      <c r="C45" s="12"/>
+      <c r="D45" s="10">
         <f>((C45)*(H45)*(I45))/(G45*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="10">
         <f>D45/10000</f>
         <v>0</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="13">
         <f>digestion_page!B40</f>
         <v>0</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="13">
         <f>digestion_page!C40</f>
         <v>0</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="13">
         <f>(LEFT(B45,FIND("/",B45)-1)/RIGHT(B45,LEN(B45)-FIND("/", B45)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="12">
+      <c r="B47" s="8"/>
+      <c r="C47" s="14">
         <f>AVERAGE(D44:D45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="13">
+      <c r="B48" s="8"/>
+      <c r="C48" s="15">
         <f>AVERAGE(E44:E45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="10"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="11"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="13">
+      <c r="B50" s="8"/>
+      <c r="C50" s="15">
         <f>AVERAGE(E44:E45)*(C49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -1709,6 +1722,31 @@
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C53:F55"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:F40">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(C40))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C51:F51">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(C51))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1731,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1743,9 +1781,10 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
@@ -1775,20 +1814,20 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="8">
+      <c r="E7" s="10">
         <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
         <v>0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <f>1-(E7/100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
@@ -1815,24 +1854,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="8">
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
         <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="10">
         <f>D11/10000</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="13">
         <f>digestion_page!B19</f>
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="13">
         <f>digestion_page!C19</f>
         <v>0</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="13">
         <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
         <v>0</v>
       </c>
@@ -1845,80 +1884,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="8">
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
         <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="10">
         <f>D12/10000</f>
         <v>0</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="13">
         <f>digestion_page!B20</f>
         <v>0</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="13">
         <f>digestion_page!C20</f>
         <v>0</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="13">
         <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="12">
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
         <f>AVERAGE(D11:D12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="13">
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
         <f>AVERAGE(E11:E12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="13">
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
         <f>AVERAGE(E11:E12)*(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
@@ -1945,24 +1984,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8">
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
         <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="10">
         <f>D22/10000</f>
         <v>0</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="13">
         <f>digestion_page!B19</f>
         <v>0</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="13">
         <f>digestion_page!C19</f>
         <v>0</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="13">
         <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
         <v>0</v>
       </c>
@@ -1975,80 +2014,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8">
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
         <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="10">
         <f>D23/10000</f>
         <v>0</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="13">
         <f>digestion_page!B20</f>
         <v>0</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="13">
         <f>digestion_page!C20</f>
         <v>0</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="13">
         <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="12">
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
         <f>AVERAGE(D22:D23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="13">
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
         <f>AVERAGE(E22:E23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="10"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="13">
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
         <f>AVERAGE(E22:E23)*(C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="11"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
@@ -2075,24 +2114,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="8">
+      <c r="C33" s="12"/>
+      <c r="D33" s="10">
         <f>((C33)*(H33)*(I33))/(G33*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="10">
         <f>D33/10000</f>
         <v>0</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="13">
         <f>digestion_page!B28</f>
         <v>0</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="13">
         <f>digestion_page!C28</f>
         <v>0</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="13">
         <f>(LEFT(B33,FIND("/",B33)-1)/RIGHT(B33,LEN(B33)-FIND("/", B33)))</f>
         <v>0</v>
       </c>
@@ -2105,80 +2144,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="8">
+      <c r="C34" s="12"/>
+      <c r="D34" s="10">
         <f>((C34)*(H34)*(I34))/(G34*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="10">
         <f>D34/10000</f>
         <v>0</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="13">
         <f>digestion_page!B29</f>
         <v>0</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="13">
         <f>digestion_page!C29</f>
         <v>0</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="13">
         <f>(LEFT(B34,FIND("/",B34)-1)/RIGHT(B34,LEN(B34)-FIND("/", B34)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="12">
+      <c r="B36" s="8"/>
+      <c r="C36" s="14">
         <f>AVERAGE(D33:D34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="13">
+      <c r="B37" s="8"/>
+      <c r="C37" s="15">
         <f>AVERAGE(E33:E34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="10"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="13">
+      <c r="B39" s="8"/>
+      <c r="C39" s="15">
         <f>AVERAGE(E33:E34)*(C38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="10"/>
+      <c r="B42" s="11"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
@@ -2205,24 +2244,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="8">
+      <c r="C44" s="12"/>
+      <c r="D44" s="10">
         <f>((C44)*(H44)*(I44))/(G44*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="10">
         <f>D44/10000</f>
         <v>0</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="13">
         <f>digestion_page!B28</f>
         <v>0</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="13">
         <f>digestion_page!C28</f>
         <v>0</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="13">
         <f>(LEFT(B44,FIND("/",B44)-1)/RIGHT(B44,LEN(B44)-FIND("/", B44)))</f>
         <v>0</v>
       </c>
@@ -2235,95 +2274,95 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="8">
+      <c r="C45" s="12"/>
+      <c r="D45" s="10">
         <f>((C45)*(H45)*(I45))/(G45*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="10">
         <f>D45/10000</f>
         <v>0</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="13">
         <f>digestion_page!B29</f>
         <v>0</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="13">
         <f>digestion_page!C29</f>
         <v>0</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="13">
         <f>(LEFT(B45,FIND("/",B45)-1)/RIGHT(B45,LEN(B45)-FIND("/", B45)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="12">
+      <c r="B47" s="8"/>
+      <c r="C47" s="14">
         <f>AVERAGE(D44:D45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="13">
+      <c r="B48" s="8"/>
+      <c r="C48" s="15">
         <f>AVERAGE(E44:E45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="10"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="11"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="13">
+      <c r="B50" s="8"/>
+      <c r="C50" s="15">
         <f>AVERAGE(E44:E45)*(C49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -2357,6 +2396,31 @@
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C53:F55"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:F40">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(C40))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C51:F51">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(C51))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2379,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2391,9 +2455,10 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
@@ -2423,20 +2488,20 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="8">
+      <c r="E7" s="10">
         <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
         <v>0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <f>1-(E7/100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
@@ -2463,24 +2528,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="8">
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
         <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="10">
         <f>D11/10000</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="13">
         <f>digestion_page!B30</f>
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="13">
         <f>digestion_page!C30</f>
         <v>0</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="13">
         <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
         <v>0</v>
       </c>
@@ -2493,80 +2558,80 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="8">
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
         <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="10">
         <f>D12/10000</f>
         <v>0</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="13">
         <f>digestion_page!B31</f>
         <v>0</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="13">
         <f>digestion_page!C31</f>
         <v>0</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="13">
         <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="12">
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
         <f>AVERAGE(D11:D12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="13">
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
         <f>AVERAGE(E11:E12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="13">
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
         <f>AVERAGE(E11:E12)*(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
@@ -2593,24 +2658,24 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8">
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
         <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="10">
         <f>D22/10000</f>
         <v>0</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="13">
         <f>digestion_page!B30</f>
         <v>0</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="13">
         <f>digestion_page!C30</f>
         <v>0</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="13">
         <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
         <v>0</v>
       </c>
@@ -2623,95 +2688,95 @@
         <f>"1/1"</f>
         <v>0</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8">
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
         <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="10">
         <f>D23/10000</f>
         <v>0</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="13">
         <f>digestion_page!B31</f>
         <v>0</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="13">
         <f>digestion_page!C31</f>
         <v>0</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="13">
         <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="12">
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
         <f>AVERAGE(D22:D23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="13">
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
         <f>AVERAGE(E22:E23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="10"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="13">
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
         <f>AVERAGE(E22:E23)*(C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="33" spans="3:6">
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2731,6 +2796,21 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F33"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2744,67 +2824,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="18" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="18" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="18" t="s">
         <v>95</v>
       </c>
     </row>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -1,41 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\request_template\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD3B338-AC2D-47F9-B79E-46A65F62DF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200127647" sheetId="2" r:id="rId2"/>
-    <sheet name="formula_page" sheetId="3" r:id="rId3"/>
+    <sheet name="200127788" sheetId="2" r:id="rId2"/>
+    <sheet name="200127789" sheetId="3" r:id="rId3"/>
+    <sheet name="200127790" sheetId="4" r:id="rId4"/>
+    <sheet name="200127791" sheetId="5" r:id="rId5"/>
+    <sheet name="formula_page" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="75">
   <si>
     <t>Date:</t>
   </si>
@@ -43,16 +27,16 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>100048453</t>
-  </si>
-  <si>
-    <t>Katanax</t>
+    <t>100048492</t>
+  </si>
+  <si>
+    <t>Microwave</t>
   </si>
   <si>
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Fe</t>
+    <t>Co, Pt</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -61,6 +45,30 @@
     <t>Acid Cocktail</t>
   </si>
   <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Vessel</t>
+  </si>
+  <si>
+    <t>Stir</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>Power (W)</t>
+  </si>
+  <si>
+    <t>T1 (°C)</t>
+  </si>
+  <si>
+    <t>T2 (°C)</t>
+  </si>
+  <si>
+    <t>P (bar)</t>
+  </si>
+  <si>
     <t>sample(s)</t>
   </si>
   <si>
@@ -70,45 +78,135 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>200127647_1</t>
-  </si>
-  <si>
-    <t>200127647_2</t>
-  </si>
-  <si>
-    <t>Fe ICP analysis</t>
+    <t>200127788_1</t>
+  </si>
+  <si>
+    <t>200127788_2</t>
+  </si>
+  <si>
+    <t>200127789_1</t>
+  </si>
+  <si>
+    <t>200127789_2</t>
+  </si>
+  <si>
+    <t>200127790_1</t>
+  </si>
+  <si>
+    <t>200127790_2</t>
+  </si>
+  <si>
+    <t>200127791_1</t>
+  </si>
+  <si>
+    <t>200127791_2</t>
+  </si>
+  <si>
+    <t>Hotplate</t>
+  </si>
+  <si>
+    <t>Cr2O3</t>
+  </si>
+  <si>
+    <t>Cocktail</t>
+  </si>
+  <si>
+    <t>LOI temp:</t>
   </si>
   <si>
     <t>sample</t>
   </si>
   <si>
+    <t>crucible (g)</t>
+  </si>
+  <si>
+    <t>crucible + sample (g)</t>
+  </si>
+  <si>
+    <t>LOI (%)</t>
+  </si>
+  <si>
+    <t>correction</t>
+  </si>
+  <si>
+    <t>200127788</t>
+  </si>
+  <si>
+    <t>Co ICP analysis</t>
+  </si>
+  <si>
     <t>Dilution</t>
   </si>
   <si>
     <t>conc. [mg/L]</t>
   </si>
   <si>
-    <t>Fe_ppm</t>
-  </si>
-  <si>
-    <t>%Fe</t>
-  </si>
-  <si>
-    <t>fe result:</t>
-  </si>
-  <si>
-    <t>fe oxide factor:</t>
-  </si>
-  <si>
-    <t>fe oxide result:</t>
-  </si>
-  <si>
-    <t>fe lot:</t>
+    <t>Co_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Co [dried]</t>
+  </si>
+  <si>
+    <t>co result:</t>
+  </si>
+  <si>
+    <t>co oxide factor:</t>
+  </si>
+  <si>
+    <t>co oxide result:</t>
+  </si>
+  <si>
+    <t>co lot:</t>
+  </si>
+  <si>
+    <t>Pt ICP analysis</t>
+  </si>
+  <si>
+    <t>Pt_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Pt [dried]</t>
+  </si>
+  <si>
+    <t>pt result:</t>
+  </si>
+  <si>
+    <t>pt oxide factor:</t>
+  </si>
+  <si>
+    <t>pt oxide result:</t>
+  </si>
+  <si>
+    <t>pt lot:</t>
+  </si>
+  <si>
+    <t>Cr2O3 titration analysis</t>
+  </si>
+  <si>
+    <t>titrant_volume (mL)</t>
+  </si>
+  <si>
+    <t>%Cr2O3 [dried]</t>
+  </si>
+  <si>
+    <t>FAS:</t>
+  </si>
+  <si>
+    <t>reported result:</t>
   </si>
   <si>
     <t>Note(s):</t>
   </si>
   <si>
+    <t>200127789</t>
+  </si>
+  <si>
+    <t>200127790</t>
+  </si>
+  <si>
+    <t>200127791</t>
+  </si>
+  <si>
     <t>A = crucible</t>
   </si>
   <si>
@@ -146,26 +244,22 @@
   </si>
   <si>
     <t>%Cr(III) = total_Cr - Cr(VI)</t>
-  </si>
-  <si>
-    <t>50 mL 1:1 HCl</t>
-  </si>
-  <si>
-    <t>Manufacturer: Assurance, 28-75FEY exp: 2026-07-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="######&quot; °C&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,18 +300,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -247,48 +335,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,21 +385,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -355,7 +429,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -389,7 +463,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -424,10 +497,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -600,24 +672,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -625,104 +699,305 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5">
-        <v>0.30449999999999999</v>
-      </c>
-      <c r="C10" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
-        <v>0.30580000000000002</v>
-      </c>
-      <c r="C11" s="4">
-        <v>250</v>
-      </c>
+      <c r="C12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C13" s="5">
+        <v>180</v>
+      </c>
+      <c r="D13" s="5">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="5">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1500</v>
+      </c>
+      <c r="C14" s="5">
+        <v>240</v>
+      </c>
+      <c r="D14" s="5">
+        <v>65</v>
+      </c>
+      <c r="E14" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
+  <mergeCells count="11">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -730,173 +1005,447 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <f>digestion_page!B17</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <f>digestion_page!C17</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <f>digestion_page!B18</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <f>digestion_page!C18</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <f>digestion_page!B17</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <f>digestion_page!C17</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <f>digestion_page!B18</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <f>digestion_page!C18</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="11"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4" t="str">
-        <f>"10/9"</f>
-        <v>10/9</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8">
-        <f>((C7)*(H7)*(I7))/(G7*1)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <f>D7/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <f>digestion_page!B10</f>
-        <v>0.30449999999999999</v>
-      </c>
-      <c r="H7" s="9">
-        <f>digestion_page!C10</f>
-        <v>250</v>
-      </c>
-      <c r="I7" s="9">
-        <f>(LEFT(B7,FIND("/",B7)-1)/RIGHT(B7,LEN(B7)-FIND("/", B7)))</f>
-        <v>1.1111111111111112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="str">
-        <f>"10/9"</f>
-        <v>10/9</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8">
-        <f>((C8)*(H8)*(I8))/(G8*1)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <f>D8/10000</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <f>digestion_page!B11</f>
-        <v>0.30580000000000002</v>
-      </c>
-      <c r="H8" s="9">
-        <f>digestion_page!C11</f>
-        <v>250</v>
-      </c>
-      <c r="I8" s="9">
-        <f>(LEFT(B8,FIND("/",B8)-1)/RIGHT(B8,LEN(B8)-FIND("/", B8)))</f>
-        <v>1.1111111111111112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="C32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20">
-        <f>AVERAGE(D7:D8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="11">
-        <f>AVERAGE(E7:E8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="B33" s="7">
+        <f>G33</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="G33" s="13">
+        <f>digestion_page!B32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="11">
-        <f>AVERAGE(E7:E8)*(C12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="B34" s="7">
+        <f>G34</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="G34" s="13">
+        <f>digestion_page!B33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="11"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="14">
+        <f>AVERAGE(D33:D34)*(10000)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="15">
+        <f>AVERAGE(D33:D34)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="B40" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="19">
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F18"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C40:F42"/>
   </mergeCells>
-  <conditionalFormatting sqref="C14:F14">
+  <conditionalFormatting sqref="B5">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C14))=0</formula>
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(C36))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -904,76 +1453,1332 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <f>digestion_page!B19</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <f>digestion_page!C19</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <f>digestion_page!B20</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <f>digestion_page!C20</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <f>digestion_page!B19</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <f>digestion_page!C19</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <f>digestion_page!B20</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <f>digestion_page!C20</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="11"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="7">
+        <f>G33</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="G33" s="13">
+        <f>digestion_page!B34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="7">
+        <f>G34</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="G34" s="13">
+        <f>digestion_page!B35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="11"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="14">
+        <f>AVERAGE(D33:D34)*(10000)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="15">
+        <f>AVERAGE(D33:D34)*(1/$F$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="B40" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C40:F42"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(C36))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <f>digestion_page!B21</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <f>digestion_page!C21</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <f>digestion_page!B22</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <f>digestion_page!C22</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <f>digestion_page!B21</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <f>digestion_page!C21</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <f>digestion_page!B22</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <f>digestion_page!C22</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <f>1-(E7/100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <f>D11/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <f>digestion_page!B23</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <f>digestion_page!C23</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <f>D12/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <f>digestion_page!B24</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <f>digestion_page!C24</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="14">
+        <f>AVERAGE(D11:D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15">
+        <f>AVERAGE(E11:E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="15">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
+        <f>((C22)*(H22)*(I22))/(G22*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <f>D22/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <f>digestion_page!B23</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <f>digestion_page!C23</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <f>(LEFT(B22,FIND("/",B22)-1)/RIGHT(B22,LEN(B22)-FIND("/", B22)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="10">
+        <f>((C23)*(H23)*(I23))/(G23*$F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <f>D23/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <f>digestion_page!B24</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <f>digestion_page!C24</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <f>(LEFT(B23,FIND("/",B23)-1)/RIGHT(B23,LEN(B23)-FIND("/", B23)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="14">
+        <f>AVERAGE(D22:D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15">
+        <f>AVERAGE(E22:E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="15">
+        <f>AVERAGE(E22:E23)*(C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:F18">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:F29">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>36</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -1,41 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\request_template\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ED252F-C158-480B-BF0E-5006B7E5957D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200127806" sheetId="2" r:id="rId2"/>
+    <sheet name="200126511" sheetId="2" r:id="rId2"/>
     <sheet name="formula_page" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t>Date:</t>
   </si>
@@ -43,7 +24,7 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>100048499</t>
+    <t>test</t>
   </si>
   <si>
     <t>Hotplate</t>
@@ -52,7 +33,7 @@
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Al</t>
+    <t>Cr3</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -70,40 +51,52 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>200127806_1</t>
-  </si>
-  <si>
-    <t>200127806_2</t>
-  </si>
-  <si>
-    <t>Al ICP analysis</t>
+    <t>200126511_1</t>
+  </si>
+  <si>
+    <t>200126511_2</t>
+  </si>
+  <si>
+    <t>cr2O3</t>
+  </si>
+  <si>
+    <t>Cr(VI)</t>
+  </si>
+  <si>
+    <t>cr2O3 titration analysis</t>
   </si>
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>Dilution</t>
-  </si>
-  <si>
-    <t>conc. [mg/L]</t>
-  </si>
-  <si>
-    <t>Al_ppm</t>
-  </si>
-  <si>
-    <t>%Al</t>
-  </si>
-  <si>
-    <t>al result:</t>
-  </si>
-  <si>
-    <t>al oxide factor:</t>
-  </si>
-  <si>
-    <t>al oxide result:</t>
-  </si>
-  <si>
-    <t>al lot:</t>
+    <t>titrant_volume (mL)</t>
+  </si>
+  <si>
+    <t>%cr2O3</t>
+  </si>
+  <si>
+    <t>FAS:</t>
+  </si>
+  <si>
+    <t>cr2O3 result:</t>
+  </si>
+  <si>
+    <t>Cr(VI) titration analysis</t>
+  </si>
+  <si>
+    <t>%Cr(VI)</t>
+  </si>
+  <si>
+    <t>Cr(VI) result:</t>
+  </si>
+  <si>
+    <t>Cr3 titration analysis</t>
+  </si>
+  <si>
+    <t>200126511</t>
+  </si>
+  <si>
+    <t>Cr3 result:</t>
   </si>
   <si>
     <t>Note(s):</t>
@@ -146,29 +139,19 @@
   </si>
   <si>
     <t>%Cr(III) = total_Cr - Cr(VI)</t>
-  </si>
-  <si>
-    <t>HF-off</t>
-  </si>
-  <si>
-    <t>25 mL HF then 50 mL HCl</t>
-  </si>
-  <si>
-    <t>Manufacturer: Assurance, 27-171ALT exp: 2026-07-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,18 +192,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -250,51 +227,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -309,21 +270,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -361,7 +314,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -395,7 +348,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -430,10 +382,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -606,24 +557,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -631,106 +582,210 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="15"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="15"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5">
-        <v>0.1019</v>
-      </c>
-      <c r="C10" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
-        <v>0.10580000000000001</v>
-      </c>
-      <c r="C11" s="4">
-        <v>250</v>
-      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -738,179 +793,254 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f>"50/6"</f>
-        <v>50/6</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1.7030000000000001</v>
-      </c>
-      <c r="D7" s="8">
-        <f>((C7)*(H7)*(I7))/(G7*1)</f>
-        <v>34817.631665031076</v>
-      </c>
-      <c r="E7" s="8">
-        <f>D7/10000</f>
-        <v>3.4817631665031077</v>
-      </c>
-      <c r="G7" s="9">
-        <f>digestion_page!B10</f>
-        <v>0.1019</v>
-      </c>
-      <c r="H7" s="9">
-        <f>digestion_page!C10</f>
-        <v>250</v>
-      </c>
-      <c r="I7" s="9">
-        <f>(LEFT(B7,FIND("/",B7)-1)/RIGHT(B7,LEN(B7)-FIND("/", B7)))</f>
-        <v>8.3333333333333339</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="G7" s="8">
+        <f>digestion_page!B19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f>"50/6"</f>
-        <v>50/6</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1.7689999999999999</v>
-      </c>
-      <c r="D8" s="8">
-        <f>((C8)*(H8)*(I8))/(G8*1)</f>
-        <v>34833.805923125394</v>
-      </c>
-      <c r="E8" s="8">
-        <f>D8/10000</f>
-        <v>3.4833805923125394</v>
-      </c>
-      <c r="G8" s="9">
-        <f>digestion_page!B11</f>
-        <v>0.10580000000000001</v>
-      </c>
-      <c r="H8" s="9">
-        <f>digestion_page!C11</f>
-        <v>250</v>
-      </c>
-      <c r="I8" s="9">
-        <f>(LEFT(B8,FIND("/",B8)-1)/RIGHT(B8,LEN(B8)-FIND("/", B8)))</f>
-        <v>8.3333333333333339</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="G8" s="8">
+        <f>digestion_page!B20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="11">
-        <f>AVERAGE(D7:D8)</f>
-        <v>34825.718794078231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="8">
+        <f>digestion_page!B28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="G17" s="8">
+        <f>digestion_page!B29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="12">
-        <f>AVERAGE(E7:E8)</f>
-        <v>3.4825718794078235</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="6">
-        <v>1.889</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21">
-        <f>AVERAGE(E7:E8)*(C12)</f>
-        <v>6.5785782802013788</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="11">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="5">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F18"/>
+  <mergeCells count="12">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
   </mergeCells>
-  <conditionalFormatting sqref="C14:F14">
+  <conditionalFormatting sqref="C10">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C14))=0</formula>
+      <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -918,76 +1048,76 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" s="13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\request_template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5088E1A-1AC3-4386-8C08-DD01E510F2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200126511" sheetId="2" r:id="rId2"/>
+    <sheet name="200127806" sheetId="2" r:id="rId2"/>
     <sheet name="formula_page" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>Date:</t>
   </si>
@@ -24,7 +43,7 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>test</t>
+    <t>100048499</t>
   </si>
   <si>
     <t>Hotplate</t>
@@ -33,7 +52,7 @@
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Cr3</t>
+    <t>Al</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -51,52 +70,58 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>200126511_1</t>
-  </si>
-  <si>
-    <t>200126511_2</t>
-  </si>
-  <si>
-    <t>cr2O3</t>
-  </si>
-  <si>
-    <t>Cr(VI)</t>
-  </si>
-  <si>
-    <t>cr2O3 titration analysis</t>
+    <t>200127806_1</t>
+  </si>
+  <si>
+    <t>200127806_2</t>
+  </si>
+  <si>
+    <t>LOI temp:</t>
   </si>
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>titrant_volume (mL)</t>
-  </si>
-  <si>
-    <t>%cr2O3</t>
-  </si>
-  <si>
-    <t>FAS:</t>
-  </si>
-  <si>
-    <t>cr2O3 result:</t>
-  </si>
-  <si>
-    <t>Cr(VI) titration analysis</t>
-  </si>
-  <si>
-    <t>%Cr(VI)</t>
-  </si>
-  <si>
-    <t>Cr(VI) result:</t>
-  </si>
-  <si>
-    <t>Cr3 titration analysis</t>
-  </si>
-  <si>
-    <t>200126511</t>
-  </si>
-  <si>
-    <t>Cr3 result:</t>
+    <t>crucible (g)</t>
+  </si>
+  <si>
+    <t>crucible + sample (g)</t>
+  </si>
+  <si>
+    <t>LOI (%)</t>
+  </si>
+  <si>
+    <t>correction</t>
+  </si>
+  <si>
+    <t>200127806</t>
+  </si>
+  <si>
+    <t>Al ICP analysis</t>
+  </si>
+  <si>
+    <t>Dilution</t>
+  </si>
+  <si>
+    <t>conc. [mg/L]</t>
+  </si>
+  <si>
+    <t>Al_ppm [dried]</t>
+  </si>
+  <si>
+    <t>%Al [dried]</t>
+  </si>
+  <si>
+    <t>al result:</t>
+  </si>
+  <si>
+    <t>al oxide factor:</t>
+  </si>
+  <si>
+    <t>al oxide result:</t>
+  </si>
+  <si>
+    <t>al lot:</t>
   </si>
   <si>
     <t>Note(s):</t>
@@ -139,19 +164,30 @@
   </si>
   <si>
     <t>%Cr(III) = total_Cr - Cr(VI)</t>
+  </si>
+  <si>
+    <t>25 mL HF then 50 mL HCl</t>
+  </si>
+  <si>
+    <t>HF-off</t>
+  </si>
+  <si>
+    <t>Manufacturer: Assurance, 27-171ALT exp: 2026-07-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="######&quot; °C&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,12 +228,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -227,40 +269,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -270,13 +336,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -314,7 +388,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -348,6 +422,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -382,9 +457,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -557,16 +633,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +650,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -582,202 +658,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="B10" s="5">
+        <v>0.1019</v>
+      </c>
+      <c r="C10" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="5"/>
+      <c r="B11" s="5">
+        <v>0.10580000000000001</v>
+      </c>
+      <c r="C11" s="4">
+        <v>250</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,7 +757,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -793,254 +765,235 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="str">
+        <f>"after "&amp;B5&amp;" °C"</f>
+        <v>after 900 °C</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4">
+        <v>27.0137</v>
+      </c>
+      <c r="C7" s="4">
+        <v>29.0304</v>
+      </c>
+      <c r="D7" s="4">
+        <v>28.898</v>
+      </c>
+      <c r="E7" s="8">
+        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
+        <v>6.5651807408142266</v>
+      </c>
+      <c r="F7" s="5">
+        <f>1-(E7/100)</f>
+        <v>0.93434819259185775</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6">
-        <f>G7</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="G7" s="8">
-        <f>digestion_page!B19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+      <c r="B11" s="4" t="str">
+        <f>"50/6"</f>
+        <v>50/6</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.7030000000000001</v>
+      </c>
+      <c r="D11" s="8">
+        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
+        <v>37264.086280777046</v>
+      </c>
+      <c r="E11" s="8">
+        <f>D11/10000</f>
+        <v>3.7264086280777047</v>
+      </c>
+      <c r="G11" s="11">
+        <f>digestion_page!B10</f>
+        <v>0.1019</v>
+      </c>
+      <c r="H11" s="11">
+        <f>digestion_page!C10</f>
+        <v>250</v>
+      </c>
+      <c r="I11" s="11">
+        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="8">
-        <f>digestion_page!B20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="7"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6">
-        <f>G16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="G16" s="8">
-        <f>digestion_page!B28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="6">
-        <f>G17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="G17" s="8">
-        <f>digestion_page!B29</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10">
-        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11">
-        <f>AVERAGE(D16:D17)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
+      <c r="B12" s="4" t="str">
+        <f>"50/6"</f>
+        <v>50/6</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1.7689999999999999</v>
+      </c>
+      <c r="D12" s="8">
+        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
+        <v>37281.397020202196</v>
+      </c>
+      <c r="E12" s="8">
+        <f>D12/10000</f>
+        <v>3.7281397020202194</v>
+      </c>
+      <c r="G12" s="11">
+        <f>digestion_page!B11</f>
+        <v>0.10580000000000001</v>
+      </c>
+      <c r="H12" s="11">
+        <f>digestion_page!C11</f>
+        <v>250</v>
+      </c>
+      <c r="I12" s="11">
+        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="5">
-        <f>C12</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>C21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="12">
+        <f>AVERAGE(D11:D12)</f>
+        <v>37272.741650489625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="13">
+        <f>AVERAGE(E11:E12)</f>
+        <v>3.727274165048962</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10">
-        <f>(C12-C21)*(10000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11">
-        <f>(C12-C21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="9" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="9">
+        <v>1.889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22">
+        <f>AVERAGE(E11:E12)*(C16)</f>
+        <v>7.0408208977774898</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="8">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F22"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C10))=0</formula>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
+      <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
+  <conditionalFormatting sqref="C18:F18">
     <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(C19))=0</formula>
+      <formula>LEN(TRIM(C18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1048,76 +1001,76 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="13" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="13" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="13" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="13" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="13" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="13" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="13" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -1,41 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\request_template\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5088E1A-1AC3-4386-8C08-DD01E510F2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200127806" sheetId="2" r:id="rId2"/>
-    <sheet name="formula_page" sheetId="3" r:id="rId3"/>
+    <sheet name="200126511" sheetId="2" r:id="rId2"/>
+    <sheet name="200126512" sheetId="3" r:id="rId3"/>
+    <sheet name="200126513" sheetId="4" r:id="rId4"/>
+    <sheet name="formula_page" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="47">
   <si>
     <t>Date:</t>
   </si>
@@ -43,7 +26,7 @@
     <t>Request ID:</t>
   </si>
   <si>
-    <t>100048499</t>
+    <t>test</t>
   </si>
   <si>
     <t>Hotplate</t>
@@ -52,7 +35,7 @@
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Al</t>
+    <t>Cr3</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -70,63 +53,75 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>200127806_1</t>
-  </si>
-  <si>
-    <t>200127806_2</t>
-  </si>
-  <si>
-    <t>LOI temp:</t>
+    <t>200126511_1</t>
+  </si>
+  <si>
+    <t>200126511_2</t>
+  </si>
+  <si>
+    <t>200126512_1</t>
+  </si>
+  <si>
+    <t>200126512_2</t>
+  </si>
+  <si>
+    <t>200126513_1</t>
+  </si>
+  <si>
+    <t>200126513_2</t>
+  </si>
+  <si>
+    <t>Cr6</t>
+  </si>
+  <si>
+    <t>Cr2O3</t>
+  </si>
+  <si>
+    <t>Cr2O3 titration analysis</t>
   </si>
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>crucible (g)</t>
-  </si>
-  <si>
-    <t>crucible + sample (g)</t>
-  </si>
-  <si>
-    <t>LOI (%)</t>
-  </si>
-  <si>
-    <t>correction</t>
-  </si>
-  <si>
-    <t>200127806</t>
-  </si>
-  <si>
-    <t>Al ICP analysis</t>
-  </si>
-  <si>
-    <t>Dilution</t>
-  </si>
-  <si>
-    <t>conc. [mg/L]</t>
-  </si>
-  <si>
-    <t>Al_ppm [dried]</t>
-  </si>
-  <si>
-    <t>%Al [dried]</t>
-  </si>
-  <si>
-    <t>al result:</t>
-  </si>
-  <si>
-    <t>al oxide factor:</t>
-  </si>
-  <si>
-    <t>al oxide result:</t>
-  </si>
-  <si>
-    <t>al lot:</t>
+    <t>titrant_volume (mL)</t>
+  </si>
+  <si>
+    <t>%Cr2O3</t>
+  </si>
+  <si>
+    <t>FAS:</t>
+  </si>
+  <si>
+    <t>cr2o3 result:</t>
+  </si>
+  <si>
+    <t>Cr6 titration analysis</t>
+  </si>
+  <si>
+    <t>%Cr6</t>
+  </si>
+  <si>
+    <t>cr6 result:</t>
+  </si>
+  <si>
+    <t>Cr3 titration analysis</t>
+  </si>
+  <si>
+    <t>200126511</t>
+  </si>
+  <si>
+    <t>cr3 result:</t>
   </si>
   <si>
     <t>Note(s):</t>
   </si>
   <si>
+    <t>200126512</t>
+  </si>
+  <si>
+    <t>200126513</t>
+  </si>
+  <si>
     <t>A = crucible</t>
   </si>
   <si>
@@ -164,30 +159,19 @@
   </si>
   <si>
     <t>%Cr(III) = total_Cr - Cr(VI)</t>
-  </si>
-  <si>
-    <t>25 mL HF then 50 mL HCl</t>
-  </si>
-  <si>
-    <t>HF-off</t>
-  </si>
-  <si>
-    <t>Manufacturer: Assurance, 27-171ALT exp: 2026-07-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="######&quot; °C&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,18 +212,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -269,64 +247,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -336,21 +290,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -388,7 +334,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -422,7 +368,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -457,10 +402,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,16 +577,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +594,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -658,98 +602,286 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5">
-        <v>0.1019</v>
-      </c>
-      <c r="C10" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
-        <v>0.10580000000000001</v>
-      </c>
-      <c r="C11" s="4">
-        <v>250</v>
-      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +889,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -765,235 +897,254 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="7">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="str">
-        <f>"after "&amp;B5&amp;" °C"</f>
-        <v>after 900 °C</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4">
-        <v>27.0137</v>
-      </c>
-      <c r="C7" s="4">
-        <v>29.0304</v>
-      </c>
-      <c r="D7" s="4">
-        <v>28.898</v>
-      </c>
-      <c r="E7" s="8">
-        <f>(((C7-B7)-(D7-B7))/(C7-B7))*100</f>
-        <v>6.5651807408142266</v>
-      </c>
-      <c r="F7" s="5">
-        <f>1-(E7/100)</f>
-        <v>0.93434819259185775</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="G7" s="8">
+        <f>digestion_page!B36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="G8" s="8">
+        <f>digestion_page!B37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="str">
-        <f>"50/6"</f>
-        <v>50/6</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1.7030000000000001</v>
-      </c>
-      <c r="D11" s="8">
-        <f>((C11)*(H11)*(I11))/(G11*$F$7)</f>
-        <v>37264.086280777046</v>
-      </c>
-      <c r="E11" s="8">
-        <f>D11/10000</f>
-        <v>3.7264086280777047</v>
-      </c>
-      <c r="G11" s="11">
-        <f>digestion_page!B10</f>
-        <v>0.1019</v>
-      </c>
-      <c r="H11" s="11">
-        <f>digestion_page!C10</f>
-        <v>250</v>
-      </c>
-      <c r="I11" s="11">
-        <f>(LEFT(B11,FIND("/",B11)-1)/RIGHT(B11,LEN(B11)-FIND("/", B11)))</f>
-        <v>8.3333333333333339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="8">
+        <f>digestion_page!B23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4" t="str">
-        <f>"50/6"</f>
-        <v>50/6</v>
-      </c>
-      <c r="C12" s="10">
-        <v>1.7689999999999999</v>
-      </c>
-      <c r="D12" s="8">
-        <f>((C12)*(H12)*(I12))/(G12*$F$7)</f>
-        <v>37281.397020202196</v>
-      </c>
-      <c r="E12" s="8">
-        <f>D12/10000</f>
-        <v>3.7281397020202194</v>
-      </c>
-      <c r="G12" s="11">
-        <f>digestion_page!B11</f>
-        <v>0.10580000000000001</v>
-      </c>
-      <c r="H12" s="11">
-        <f>digestion_page!C11</f>
-        <v>250</v>
-      </c>
-      <c r="I12" s="11">
-        <f>(LEFT(B12,FIND("/",B12)-1)/RIGHT(B12,LEN(B12)-FIND("/", B12)))</f>
-        <v>8.3333333333333339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="12">
-        <f>AVERAGE(D11:D12)</f>
-        <v>37272.741650489625</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="13">
-        <f>AVERAGE(E11:E12)</f>
-        <v>3.727274165048962</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="G17" s="8">
+        <f>digestion_page!B24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="11">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="9">
-        <v>1.889</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="22">
-        <f>AVERAGE(E11:E12)*(C16)</f>
-        <v>7.0408208977774898</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
+      <c r="B25" s="5">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F22"/>
-    <mergeCell ref="A9:B9"/>
+  <mergeCells count="12">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
-      <formula>LEN(TRIM(B5))=0</formula>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:F18">
+  <conditionalFormatting sqref="C19">
     <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(C18))=0</formula>
+      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1001,76 +1152,638 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="G7" s="8">
+        <f>digestion_page!B38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="G8" s="8">
+        <f>digestion_page!B39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="8">
+        <f>digestion_page!B25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="G17" s="8">
+        <f>digestion_page!B26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="11">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C19))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="G7" s="8">
+        <f>digestion_page!B40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="G8" s="8">
+        <f>digestion_page!B41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="8">
+        <f>digestion_page!B27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="G17" s="8">
+        <f>digestion_page!B28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="11">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="5">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C19))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="13" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -8,17 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="200126511" sheetId="2" r:id="rId2"/>
-    <sheet name="200126512" sheetId="3" r:id="rId3"/>
-    <sheet name="200126513" sheetId="4" r:id="rId4"/>
-    <sheet name="formula_page" sheetId="5" r:id="rId5"/>
+    <sheet name="2001265" sheetId="2" r:id="rId2"/>
+    <sheet name="2001266" sheetId="3" r:id="rId3"/>
+    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t>Date:</t>
   </si>
@@ -53,22 +52,16 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>200126511_1</t>
-  </si>
-  <si>
-    <t>200126511_2</t>
-  </si>
-  <si>
-    <t>200126512_1</t>
-  </si>
-  <si>
-    <t>200126512_2</t>
-  </si>
-  <si>
-    <t>200126513_1</t>
-  </si>
-  <si>
-    <t>200126513_2</t>
+    <t>2001265_1</t>
+  </si>
+  <si>
+    <t>2001265_2</t>
+  </si>
+  <si>
+    <t>2001266_1</t>
+  </si>
+  <si>
+    <t>2001266_2</t>
   </si>
   <si>
     <t>Cr6</t>
@@ -107,7 +100,7 @@
     <t>Cr3 titration analysis</t>
   </si>
   <si>
-    <t>200126511</t>
+    <t>2001265</t>
   </si>
   <si>
     <t>cr3 result:</t>
@@ -116,10 +109,7 @@
     <t>Note(s):</t>
   </si>
   <si>
-    <t>200126512</t>
-  </si>
-  <si>
-    <t>200126513</t>
+    <t>2001266</t>
   </si>
   <si>
     <t>A = crucible</t>
@@ -578,10 +568,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -591,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -671,185 +661,143 @@
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="B21" s="6"/>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="5"/>
-    </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
+      <c r="A27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="6"/>
       <c r="C28" s="5"/>
     </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B32" s="6"/>
       <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="B33" s="6"/>
       <c r="C33" s="5"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="B34" s="6"/>
       <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="5"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="5"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="5"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -857,14 +805,14 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -886,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -899,22 +847,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -928,7 +876,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="G7" s="8">
-        <f>digestion_page!B36</f>
+        <f>digestion_page!B32</f>
         <v>0</v>
       </c>
     </row>
@@ -943,20 +891,20 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="G8" s="8">
-        <f>digestion_page!B37</f>
+        <f>digestion_page!B33</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="10">
@@ -966,7 +914,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="11">
@@ -976,22 +924,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="7"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1005,7 +953,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="G16" s="8">
-        <f>digestion_page!B23</f>
+        <f>digestion_page!B21</f>
         <v>0</v>
       </c>
     </row>
@@ -1020,20 +968,20 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="G17" s="8">
-        <f>digestion_page!B24</f>
+        <f>digestion_page!B22</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="10">
@@ -1043,7 +991,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="11">
@@ -1053,24 +1001,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B25" s="5">
         <f>C12</f>
@@ -1083,7 +1031,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="10">
@@ -1093,7 +1041,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="11">
@@ -1103,7 +1051,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="B30" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -1167,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1180,22 +1128,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1209,7 +1157,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="G7" s="8">
-        <f>digestion_page!B38</f>
+        <f>digestion_page!B34</f>
         <v>0</v>
       </c>
     </row>
@@ -1224,20 +1172,20 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="G8" s="8">
-        <f>digestion_page!B39</f>
+        <f>digestion_page!B35</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="10">
@@ -1247,7 +1195,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="11">
@@ -1257,22 +1205,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="7"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1286,7 +1234,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="G16" s="8">
-        <f>digestion_page!B25</f>
+        <f>digestion_page!B23</f>
         <v>0</v>
       </c>
     </row>
@@ -1301,20 +1249,20 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="G17" s="8">
-        <f>digestion_page!B26</f>
+        <f>digestion_page!B24</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="10">
@@ -1324,7 +1272,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="11">
@@ -1334,24 +1282,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5">
         <f>C12</f>
@@ -1364,7 +1312,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="10">
@@ -1374,7 +1322,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="11">
@@ -1384,7 +1332,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="B30" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -1434,287 +1382,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6">
-        <f>G7</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="G7" s="8">
-        <f>digestion_page!B40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="8">
-        <f>digestion_page!B41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="7"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6">
-        <f>G16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="G16" s="8">
-        <f>digestion_page!B27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6">
-        <f>G17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="G17" s="8">
-        <f>digestion_page!B28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10">
-        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11">
-        <f>AVERAGE(D16:D17)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="5">
-        <f>C12</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>C21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10">
-        <f>(C12-C21)*(10000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11">
-        <f>(C12-C21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C30:F32"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(C19))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1723,67 +1390,67 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
-    <sheet name="2001265" sheetId="2" r:id="rId2"/>
-    <sheet name="2001266" sheetId="3" r:id="rId3"/>
-    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
+    <sheet name="200126511" sheetId="2" r:id="rId2"/>
+    <sheet name="200126512" sheetId="3" r:id="rId3"/>
+    <sheet name="200126513" sheetId="4" r:id="rId4"/>
+    <sheet name="200126514" sheetId="5" r:id="rId5"/>
+    <sheet name="formula_page" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
   <si>
     <t>Date:</t>
   </si>
@@ -34,7 +36,7 @@
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Cr3</t>
+    <t>Cr6</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -52,25 +54,31 @@
     <t>volume (mL)</t>
   </si>
   <si>
-    <t>2001265_1</t>
-  </si>
-  <si>
-    <t>2001265_2</t>
-  </si>
-  <si>
-    <t>2001266_1</t>
-  </si>
-  <si>
-    <t>2001266_2</t>
-  </si>
-  <si>
-    <t>Cr6</t>
-  </si>
-  <si>
-    <t>Cr2O3</t>
-  </si>
-  <si>
-    <t>Cr2O3 titration analysis</t>
+    <t>200126511_1</t>
+  </si>
+  <si>
+    <t>200126511_2</t>
+  </si>
+  <si>
+    <t>200126512_1</t>
+  </si>
+  <si>
+    <t>200126512_2</t>
+  </si>
+  <si>
+    <t>200126513_1</t>
+  </si>
+  <si>
+    <t>200126513_2</t>
+  </si>
+  <si>
+    <t>200126514_1</t>
+  </si>
+  <si>
+    <t>200126514_2</t>
+  </si>
+  <si>
+    <t>Cr6 titration analysis</t>
   </si>
   <si>
     <t>sample</t>
@@ -79,37 +87,16 @@
     <t>titrant_volume (mL)</t>
   </si>
   <si>
-    <t>%Cr2O3</t>
+    <t>%Cr6</t>
   </si>
   <si>
     <t>FAS:</t>
   </si>
   <si>
-    <t>cr2o3 result:</t>
-  </si>
-  <si>
-    <t>Cr6 titration analysis</t>
-  </si>
-  <si>
-    <t>%Cr6</t>
-  </si>
-  <si>
     <t>cr6 result:</t>
   </si>
   <si>
-    <t>Cr3 titration analysis</t>
-  </si>
-  <si>
-    <t>2001265</t>
-  </si>
-  <si>
-    <t>cr3 result:</t>
-  </si>
-  <si>
     <t>Note(s):</t>
-  </si>
-  <si>
-    <t>2001266</t>
   </si>
   <si>
     <t>A = crucible</t>
@@ -155,11 +142,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -237,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -252,14 +241,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -568,10 +559,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -661,158 +652,40 @@
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
+    </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="5"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="5"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -820,13 +693,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -847,22 +720,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -873,10 +746,10 @@
         <f>G7</f>
         <v>0</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="G7" s="8">
-        <f>digestion_page!B32</f>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="G7" s="10">
+        <f>digestion_page!B10</f>
         <v>0</v>
       </c>
     </row>
@@ -888,211 +761,72 @@
         <f>G8</f>
         <v>0</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="8">
-        <f>digestion_page!B33</f>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="G8" s="10">
+        <f>digestion_page!B11</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="9"/>
+      <c r="A10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="11"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
         <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11">
+      <c r="A12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="13">
         <f>AVERAGE(D7:D8)*(1/1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6">
-        <f>G16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="G16" s="8">
-        <f>digestion_page!B21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="6">
-        <f>G17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="G17" s="8">
-        <f>digestion_page!B22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10">
-        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11">
-        <f>AVERAGE(D16:D17)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="5">
-        <f>C12</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>C21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10">
-        <f>(C12-C21)*(10000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11">
-        <f>(C12-C21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="C14:F16"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1101,13 +835,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1128,22 +862,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1154,10 +888,10 @@
         <f>G7</f>
         <v>0</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="G7" s="8">
-        <f>digestion_page!B34</f>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="G7" s="10">
+        <f>digestion_page!B12</f>
         <v>0</v>
       </c>
     </row>
@@ -1169,211 +903,72 @@
         <f>G8</f>
         <v>0</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="8">
-        <f>digestion_page!B35</f>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="G8" s="10">
+        <f>digestion_page!B13</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="9"/>
+      <c r="A10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="11"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
         <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11">
+      <c r="A12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="13">
         <f>AVERAGE(D7:D8)*(1/1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="6">
-        <f>G16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="G16" s="8">
-        <f>digestion_page!B23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6">
-        <f>G17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="G17" s="8">
-        <f>digestion_page!B24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10">
-        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11">
-        <f>AVERAGE(D16:D17)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="5">
-        <f>C12</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>C21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10">
-        <f>(C12-C21)*(10000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11">
-        <f>(C12-C21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="C14:F16"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1382,6 +977,290 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="G7" s="10">
+        <f>digestion_page!B14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="G8" s="10">
+        <f>digestion_page!B15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="13">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C14:F16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="G7" s="10">
+        <f>digestion_page!B16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="G8" s="10">
+        <f>digestion_page!B17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
+        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="13">
+        <f>AVERAGE(D7:D8)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C14:F16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1389,68 +1268,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="13" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="13" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="13" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="13" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="13" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="15" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="13" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -10,16 +10,14 @@
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
     <sheet name="200126511" sheetId="2" r:id="rId2"/>
     <sheet name="200126512" sheetId="3" r:id="rId3"/>
-    <sheet name="200126513" sheetId="4" r:id="rId4"/>
-    <sheet name="200126514" sheetId="5" r:id="rId5"/>
-    <sheet name="formula_page" sheetId="6" r:id="rId6"/>
+    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t>Date:</t>
   </si>
@@ -36,67 +34,82 @@
     <t>Element(s)</t>
   </si>
   <si>
+    <t>Cr3</t>
+  </si>
+  <si>
+    <t>SOP#</t>
+  </si>
+  <si>
+    <t>Cocktail</t>
+  </si>
+  <si>
+    <t>sample(s)</t>
+  </si>
+  <si>
+    <t>weight (g)</t>
+  </si>
+  <si>
+    <t>volume (mL)</t>
+  </si>
+  <si>
+    <t>200126511_1</t>
+  </si>
+  <si>
+    <t>200126511_2</t>
+  </si>
+  <si>
+    <t>200126512_1</t>
+  </si>
+  <si>
+    <t>200126512_2</t>
+  </si>
+  <si>
     <t>Cr6</t>
   </si>
   <si>
-    <t>SOP#</t>
-  </si>
-  <si>
-    <t>Cocktail</t>
-  </si>
-  <si>
-    <t>sample(s)</t>
-  </si>
-  <si>
-    <t>weight (g)</t>
-  </si>
-  <si>
-    <t>volume (mL)</t>
-  </si>
-  <si>
-    <t>200126511_1</t>
-  </si>
-  <si>
-    <t>200126511_2</t>
-  </si>
-  <si>
-    <t>200126512_1</t>
-  </si>
-  <si>
-    <t>200126512_2</t>
-  </si>
-  <si>
-    <t>200126513_1</t>
-  </si>
-  <si>
-    <t>200126513_2</t>
-  </si>
-  <si>
-    <t>200126514_1</t>
-  </si>
-  <si>
-    <t>200126514_2</t>
+    <t>Cr2O3</t>
+  </si>
+  <si>
+    <t>Cr2O3 titration analysis</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>titrant_volume (mL)</t>
+  </si>
+  <si>
+    <t>%Cr2O3</t>
+  </si>
+  <si>
+    <t>FAS:</t>
+  </si>
+  <si>
+    <t>cr2o3 result:</t>
   </si>
   <si>
     <t>Cr6 titration analysis</t>
   </si>
   <si>
-    <t>sample</t>
-  </si>
-  <si>
-    <t>titrant_volume (mL)</t>
-  </si>
-  <si>
     <t>%Cr6</t>
   </si>
   <si>
-    <t>FAS:</t>
-  </si>
-  <si>
     <t>cr6 result:</t>
   </si>
   <si>
+    <t>Cr3 titration analysis</t>
+  </si>
+  <si>
+    <t>200126511</t>
+  </si>
+  <si>
+    <t>cr3 result:</t>
+  </si>
+  <si>
     <t>Note(s):</t>
+  </si>
+  <si>
+    <t>200126512</t>
   </si>
   <si>
     <t>A = crucible</t>
@@ -559,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -572,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -652,40 +665,158 @@
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
-    </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5"/>
+      <c r="A16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="C17" s="5"/>
     </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -693,13 +824,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -707,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -720,22 +851,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -749,7 +880,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="G7" s="10">
-        <f>digestion_page!B10</f>
+        <f>digestion_page!B32</f>
         <v>0</v>
       </c>
     </row>
@@ -764,20 +895,20 @@
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
       <c r="G8" s="10">
-        <f>digestion_page!B11</f>
+        <f>digestion_page!B33</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12">
@@ -787,7 +918,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="13">
@@ -796,37 +927,176 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="G16" s="10">
+        <f>digestion_page!B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="G17" s="10">
+        <f>digestion_page!B22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="13">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="13">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="12">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -835,13 +1105,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -849,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -862,22 +1132,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -891,7 +1161,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="G7" s="10">
-        <f>digestion_page!B12</f>
+        <f>digestion_page!B34</f>
         <v>0</v>
       </c>
     </row>
@@ -906,20 +1176,20 @@
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
       <c r="G8" s="10">
-        <f>digestion_page!B13</f>
+        <f>digestion_page!B35</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12">
@@ -929,7 +1199,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="13">
@@ -938,37 +1208,176 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="G16" s="10">
+        <f>digestion_page!B23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="G17" s="10">
+        <f>digestion_page!B24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12">
+        <f>AVERAGE(D16:D17)*(10000)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="13">
+        <f>AVERAGE(D16:D17)*(1/1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12">
+        <f>(C12-C21)*(10000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="13">
+        <f>(C12-C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="12">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C30:F32"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C19))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -976,290 +1385,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6">
-        <f>G7</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="G7" s="10">
-        <f>digestion_page!B14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="G8" s="10">
-        <f>digestion_page!B15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="13">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6">
-        <f>G7</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="G7" s="10">
-        <f>digestion_page!B16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="6">
-        <f>G8</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="G8" s="10">
-        <f>digestion_page!B17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12">
-        <f>AVERAGE(D7:D8)*(10000)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="13">
-        <f>AVERAGE(D7:D8)*(1/1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C14:F16"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1269,67 +1394,67 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
